--- a/wwwroot/contribution_files/metadata_template.xlsx
+++ b/wwwroot/contribution_files/metadata_template.xlsx
@@ -1844,7 +1844,7 @@
     <t>e.g. breast cancer, acute kidney disease, bacterial gastritis, inflammatory bowel disease, lactic acidosis, Asperger syndrome, congenital lactase deficiency, Wolfram syndrome, .</t>
   </si>
   <si>
-    <t xml:space="preserve">choose among one of these eight main categories (example: disease of metabolism) 
+    <t xml:space="preserve">choose among one of these nine main categories (example: disease of metabolism) 
 1. Disease of cellular proliferation (such as  neoplasms, tumors, cancers)
 2. Disease of anatomical entity (structural and functional conditions affecting specific organ systems such as cardiovascular disease, chronic kidney disease)
 3. Disease by infectious agent (viral, bacterial, fungal, and parasitic infections)
@@ -1853,6 +1853,7 @@
 6. Disease of mental health (psychiatric, behavioral, and neurodevelopmental conditions, such as major depressive disorder, schizophrenia, ADHD).
 7. Physical disorder (general or multi-system clinical conditions such as inflammation, physical trauma, sleep disorders, and immune system diseases).
 8. Syndrome (collections of clinical signs and symptoms that occur together, such as chronic fatigue syndrome, irritable bowel syndrome, metabolic syndrome).
+9. Healthy (healthy animals with no induced or spontaneous disease, including healthy controls).
 </t>
   </si>
 </sst>
